--- a/data/indicators/daily/2026-03-07_Daily.xlsx
+++ b/data/indicators/daily/2026-03-07_Daily.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicators001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sheet_a" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sheet_b" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="headerAnchor">'indicators001'!$A$1</definedName>
+    <definedName name="headerAnchor">'data_sheet_a'!$A$1,'data_sheet_b'!$A$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,4 +451,42 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>event_news_1_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>決算上方修正に関するお知らせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>材料不明・需給起因疑い</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/indicators/daily/2026-03-07_Daily.xlsx
+++ b/data/indicators/daily/2026-03-07_Daily.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sheet_a" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sheet_b" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="data_sheet_a" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data_sheet_b" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="headerAnchor">'data_sheet_a'!$A$1,'data_sheet_b'!$A$1</definedName>

--- a/data/indicators/daily/2026-03-07_Daily.xlsx
+++ b/data/indicators/daily/2026-03-07_Daily.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data_sheet_a" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="data_sheet_b" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sheet_a" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sheet_b" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="headerAnchor">'data_sheet_a'!$A$1,'data_sheet_b'!$A$1</definedName>
